--- a/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17167499-5222-42D5-940B-1A3D140B7208}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DCDED6C-FE33-4F2D-8AFC-F8789E7AE1D8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B2E026E-87C9-4B09-AAFD-11273DCAC41F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1D103DC-0612-46E0-A56C-0AD64989B8D8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2BB787A-FBE7-48BB-B0F2-A90938C0322E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45C5C71F-2C3F-4FE8-86D9-FEE1B5ACE456}"/>
 </file>